--- a/output/pdf_financials_xlsx/WIL.xlsx
+++ b/output/pdf_financials_xlsx/WIL.xlsx
@@ -1399,34 +1399,34 @@
         <v>-2.130067</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>2.951893</v>
+        <v>-2.951893</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>5.818518</v>
+        <v>-5.818518</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>2.233551</v>
+        <v>-2.233551</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>1.794954</v>
+        <v>-1.794954</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>1.703126</v>
+        <v>-1.703126</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>2.269619</v>
+        <v>-2.269619</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>1.215556</v>
+        <v>-1.215556</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>1.677471</v>
+        <v>-1.677471</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>2.316462</v>
+        <v>-2.316462</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>3.144031</v>
+        <v>-3.144031</v>
       </c>
     </row>
     <row r="17">
@@ -1715,34 +1715,34 @@
         <v>-2.130067</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>2.951893</v>
+        <v>-2.951893</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>5.818518</v>
+        <v>-5.818518</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>2.233551</v>
+        <v>-2.233551</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>1.794954</v>
+        <v>-1.794954</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>1.703126</v>
+        <v>-1.703126</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>2.269619</v>
+        <v>-2.269619</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>1.215556</v>
+        <v>-1.215556</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>1.677471</v>
+        <v>-1.677471</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>2.316462</v>
+        <v>-2.316462</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>3.144031</v>
+        <v>-3.144031</v>
       </c>
     </row>
     <row r="21">
@@ -1898,34 +1898,34 @@
         <v>-2.130067</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>2.951893</v>
+        <v>-2.951893</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>5.818518</v>
+        <v>-5.818518</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>2.233551</v>
+        <v>-2.233551</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>1.794954</v>
+        <v>-1.794954</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>1.703126</v>
+        <v>-1.703126</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>2.269619</v>
+        <v>-2.269619</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>1.215556</v>
+        <v>-1.215556</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>1.677471</v>
+        <v>-1.677471</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>2.316462</v>
+        <v>-2.316462</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>3.144031</v>
+        <v>-3.144031</v>
       </c>
     </row>
     <row r="24">
@@ -2093,34 +2093,34 @@
         <v>30.429529</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>42.1699</v>
+        <v>-42.1699</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>44.757831</v>
+        <v>-44.757831</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>55.838775</v>
+        <v>-55.838775</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>59.8318</v>
+        <v>-59.8318</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>56.770867</v>
+        <v>-56.770867</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>56.740475</v>
+        <v>-56.740475</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>60.7778</v>
+        <v>-60.7778</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>83.87354999999999</v>
+        <v>-83.87354999999999</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>77.2154</v>
+        <v>-77.2154</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>78.600775</v>
+        <v>-78.600775</v>
       </c>
     </row>
     <row r="27">
@@ -2154,34 +2154,34 @@
         <v>-2.130067</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>2.951893</v>
+        <v>-2.951893</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>5.818518</v>
+        <v>-5.818518</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>2.233551</v>
+        <v>-2.233551</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>1.794954</v>
+        <v>-1.794954</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>1.703126</v>
+        <v>-1.703126</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>2.269619</v>
+        <v>-2.269619</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>1.215556</v>
+        <v>-1.215556</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>1.677471</v>
+        <v>-1.677471</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>2.316462</v>
+        <v>-2.316462</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>3.144031</v>
+        <v>-3.144031</v>
       </c>
     </row>
     <row r="28">
@@ -2276,34 +2276,34 @@
         <v>-2.130067</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>2.951893</v>
+        <v>-2.951893</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>5.818518</v>
+        <v>-5.818518</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>2.233551</v>
+        <v>-2.233551</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>1.794954</v>
+        <v>-1.794954</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>1.703126</v>
+        <v>-1.703126</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>2.269619</v>
+        <v>-2.269619</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>1.215556</v>
+        <v>-1.215556</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>1.677471</v>
+        <v>-1.677471</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>2.316462</v>
+        <v>-2.316462</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>3.144031</v>
+        <v>-3.144031</v>
       </c>
     </row>
     <row r="30">
@@ -2434,34 +2434,34 @@
         <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -45686,10 +45686,10 @@
         </is>
       </c>
       <c r="U351" s="5" t="n">
-        <v>2.316462</v>
+        <v>-2.316462</v>
       </c>
       <c r="V351" s="5" t="n">
-        <v>3.144031</v>
+        <v>-3.144031</v>
       </c>
     </row>
     <row r="352">
@@ -46454,31 +46454,31 @@
         <v>-2.130067</v>
       </c>
       <c r="M359" s="5" t="n">
-        <v>2.951893</v>
+        <v>-2.951893</v>
       </c>
       <c r="N359" s="5" t="n">
-        <v>5.818518</v>
+        <v>-5.818518</v>
       </c>
       <c r="O359" s="5" t="n">
-        <v>2.233551</v>
+        <v>-2.233551</v>
       </c>
       <c r="P359" s="5" t="n">
-        <v>1.794954</v>
+        <v>-1.794954</v>
       </c>
       <c r="Q359" s="5" t="n">
-        <v>1.703126</v>
+        <v>-1.703126</v>
       </c>
       <c r="R359" s="5" t="n">
-        <v>2.269619</v>
+        <v>-2.269619</v>
       </c>
       <c r="S359" s="5" t="n">
-        <v>1.215556</v>
+        <v>-1.215556</v>
       </c>
       <c r="T359" s="5" t="n">
-        <v>1.677471</v>
+        <v>-1.677471</v>
       </c>
       <c r="U359" s="5" t="n">
-        <v>2.316462</v>
+        <v>-2.316462</v>
       </c>
       <c r="V359" t="inlineStr">
         <is>
@@ -47657,10 +47657,10 @@
         </is>
       </c>
       <c r="N371" s="5" t="n">
-        <v>5.818518</v>
+        <v>-5.818518</v>
       </c>
       <c r="O371" s="5" t="n">
-        <v>2.233551</v>
+        <v>-2.233551</v>
       </c>
       <c r="P371" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/WIL.xlsx
+++ b/output/pdf_financials_xlsx/WIL.xlsx
@@ -1131,16 +1131,16 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.007068</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.003873</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.004392</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.005973</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
@@ -2130,16 +2130,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.043278</v>
+        <v>-0.050346</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.397444</v>
+        <v>-0.401317</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.446172</v>
+        <v>-0.450564</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.9724930000000001</v>
+        <v>-0.9784659999999999</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-1.7521</v>
@@ -2252,16 +2252,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.043278</v>
+        <v>-0.050346</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.397444</v>
+        <v>-0.401317</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.446172</v>
+        <v>-0.450564</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.9724930000000001</v>
+        <v>-0.9784659999999999</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-1.7521</v>
@@ -2593,40 +2593,40 @@
         <v>0</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.09794600000000001</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.205439</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.31637</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.185583</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.130672</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.280923</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.275912</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.348532</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.057003</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.122051</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>1.045989</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>0.012475</v>
       </c>
     </row>
     <row r="35">
@@ -2715,40 +2715,40 @@
         <v>0.619406</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.09794600000000001</v>
+        <v>0.195892</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.205439</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.31637</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.185583</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.130672</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.280923</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.275912</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.348532</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.057003</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.122051</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>1.045989</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0</v>
+        <v>0.012475</v>
       </c>
     </row>
     <row r="37">
@@ -3450,37 +3450,37 @@
         <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.205439</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.31637</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.185583</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.133441</v>
+        <v>0.002769</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.287682</v>
+        <v>0.006759</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.338544</v>
+        <v>0.06263199999999999</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.367967</v>
+        <v>0.019435</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.072003</v>
+        <v>0.015</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.137051</v>
+        <v>0.015</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>1.045989</v>
+        <v>0</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>0.293954</v>
+        <v>0.281479</v>
       </c>
     </row>
     <row r="49">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -13800,7 +13800,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -50668,7 +50668,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
@@ -50776,7 +50776,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
@@ -51094,7 +51094,7 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E404" s="5" t="n">

--- a/output/pdf_financials_xlsx/WIL.xlsx
+++ b/output/pdf_financials_xlsx/WIL.xlsx
@@ -7338,49 +7338,49 @@
         </is>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>0.000129</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>0</v>
+        <v>0.000775</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>0</v>
+        <v>0.00242</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>0</v>
+        <v>0.00255</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>0</v>
+        <v>0.001479</v>
       </c>
       <c r="J110" s="3" t="n">
-        <v>0</v>
+        <v>0.00057</v>
       </c>
       <c r="K110" s="3" t="n">
-        <v>0</v>
+        <v>0.00066</v>
       </c>
       <c r="L110" s="3" t="n">
-        <v>0</v>
+        <v>0.002594</v>
       </c>
       <c r="M110" s="3" t="n">
-        <v>0</v>
+        <v>-0.003638</v>
       </c>
       <c r="N110" s="3" t="n">
-        <v>0</v>
+        <v>0.002883</v>
       </c>
       <c r="O110" s="3" t="n">
-        <v>0</v>
+        <v>-5.2e-05</v>
       </c>
       <c r="P110" s="3" t="n">
-        <v>0</v>
+        <v>-0.001848</v>
       </c>
       <c r="Q110" s="3" t="n">
-        <v>0</v>
+        <v>-1.7e-05</v>
       </c>
       <c r="R110" s="3" t="n">
-        <v>0</v>
+        <v>1.7e-05</v>
       </c>
       <c r="S110" s="3" t="n">
-        <v>0</v>
+        <v>-6.8e-05</v>
       </c>
     </row>
     <row r="111">
@@ -20042,7 +20042,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
           <t>-</t>
@@ -23410,7 +23414,11 @@
           <t>Accretion 9</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E139" t="inlineStr">
         <is>
           <t>-</t>
@@ -26552,7 +26560,11 @@
           <t>Accretion 8</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr"/>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E169" t="inlineStr">
         <is>
           <t>-</t>
@@ -32326,7 +32338,11 @@
           <t>8 Accretion</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr"/>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E224" t="inlineStr">
         <is>
           <t>-</t>
@@ -40958,7 +40974,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D306" t="inlineStr"/>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E306" t="inlineStr">
         <is>
           <t>-</t>
@@ -42430,7 +42450,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D320" t="inlineStr"/>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E320" t="inlineStr">
         <is>
           <t>-</t>
